--- a/Inputs/Puntos.xlsx
+++ b/Inputs/Puntos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Codigos\Extraer_CR2MET_punto\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Codigos\Extraer_CR2MET_punto\Inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{475A7F3B-B6DD-41D7-B282-C6648E8AA0DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D745415-1551-48CF-8D96-043D5E56FD9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23085" yWindow="1830" windowWidth="21600" windowHeight="13050" xr2:uid="{856FD7A7-6229-4747-8ECD-87055DB5DEB0}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{856FD7A7-6229-4747-8ECD-87055DB5DEB0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>Estacion</t>
   </si>
@@ -47,16 +47,7 @@
     <t>Longitud</t>
   </si>
   <si>
-    <t>Lautaro_Embalse</t>
-  </si>
-  <si>
-    <t>Portezuelo_El_Gaucho</t>
-  </si>
-  <si>
-    <t>Los_Loros</t>
-  </si>
-  <si>
-    <t>Iglesia_Colorada</t>
+    <t>Conay_Albaricoque</t>
   </si>
 </sst>
 </file>
@@ -428,7 +419,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE5D43C7-B3DA-4B12-8BD4-AD5990782B50}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.109375" bestFit="1" customWidth="1"/>
@@ -453,43 +444,10 @@
         <v>3</v>
       </c>
       <c r="B2">
-        <v>-27.978300000000001</v>
+        <v>-28.953099999999999</v>
       </c>
       <c r="C2">
-        <v>-70.003299999999996</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3">
-        <v>-28.623100000000001</v>
-      </c>
-      <c r="C3">
-        <v>-70.045000000000002</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>-27.831700000000001</v>
-      </c>
-      <c r="C4">
-        <v>-70.111900000000006</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5">
-        <v>-28.1572</v>
-      </c>
-      <c r="C5">
-        <v>-69.880799999999994</v>
+        <v>-70.116699999999994</v>
       </c>
     </row>
   </sheetData>
